--- a/data/raw/sales/Week 33/White_Mulberry/other_channels.xlsx
+++ b/data/raw/sales/Week 33/White_Mulberry/other_channels.xlsx
@@ -695,7 +695,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>16875.18</v>
+        <v>5625.06</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/data/raw/sales/Week 33/White_Mulberry/other_channels.xlsx
+++ b/data/raw/sales/Week 33/White_Mulberry/other_channels.xlsx
@@ -695,7 +695,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5625.06</v>
+        <v>4767</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
